--- a/data/raw/prospect_larvae_raw.xlsx
+++ b/data/raw/prospect_larvae_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aidan\Desktop\RStudio Projects\SCLTS-Deformities\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2301BB19-1D78-4518-9E6B-66F4897D1FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82736A9-C069-47B3-9CE7-A2864AD99555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>temperature</t>
   </si>
   <si>
-    <t>deformed?</t>
-  </si>
-  <si>
     <t>comments</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
   </si>
   <si>
     <t>RESAMPLE; two extra hind feet</t>
+  </si>
+  <si>
+    <t>deformed</t>
   </si>
 </sst>
 </file>
@@ -496,10 +496,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -540,30 +541,30 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1">
         <v>45431</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>5.2</v>
@@ -575,36 +576,36 @@
         <v>94</v>
       </c>
       <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
         <v>19</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>45431</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>4.9000000000000004</v>
@@ -616,36 +617,36 @@
         <v>90</v>
       </c>
       <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1">
         <v>45431</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -657,36 +658,36 @@
         <v>92</v>
       </c>
       <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
         <v>19</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
         <v>45431</v>
       </c>
       <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>3.5</v>
@@ -698,39 +699,39 @@
         <v>93</v>
       </c>
       <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
-      </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1">
         <v>45431</v>
       </c>
       <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -742,39 +743,39 @@
         <v>82</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
         <v>23</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>24</v>
-      </c>
       <c r="O6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1">
         <v>45431</v>
       </c>
       <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -786,39 +787,39 @@
         <v>95</v>
       </c>
       <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
         <v>19</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
-      </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1">
         <v>45431</v>
       </c>
       <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>4.2</v>
@@ -830,36 +831,36 @@
         <v>86</v>
       </c>
       <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
         <v>19</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>20</v>
-      </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1">
         <v>45431</v>
       </c>
       <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
-        <v>17</v>
-      </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>4.5999999999999996</v>
@@ -871,36 +872,36 @@
         <v>95</v>
       </c>
       <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
         <v>19</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1">
         <v>45431</v>
       </c>
       <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>4.2</v>
@@ -912,36 +913,36 @@
         <v>85</v>
       </c>
       <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
         <v>19</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
-      </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1">
         <v>45431</v>
       </c>
       <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>4.2</v>
@@ -953,36 +954,36 @@
         <v>95</v>
       </c>
       <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
         <v>19</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1">
         <v>45431</v>
       </c>
       <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
         <v>16</v>
       </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>3.4</v>
@@ -994,36 +995,36 @@
         <v>81</v>
       </c>
       <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
         <v>19</v>
       </c>
-      <c r="J12">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>20</v>
-      </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1">
         <v>45431</v>
       </c>
       <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13">
         <v>4.3</v>
@@ -1035,39 +1036,39 @@
         <v>92</v>
       </c>
       <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13" t="s">
         <v>19</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13" t="s">
-        <v>20</v>
-      </c>
       <c r="M13">
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1">
         <v>45431</v>
       </c>
       <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
         <v>16</v>
       </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>4.7</v>
@@ -1079,36 +1080,36 @@
         <v>85</v>
       </c>
       <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" t="s">
         <v>19</v>
       </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>20</v>
-      </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>45431</v>
       </c>
       <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
         <v>16</v>
       </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15">
         <v>4.3</v>
@@ -1120,36 +1121,36 @@
         <v>87</v>
       </c>
       <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
         <v>19</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15" t="s">
-        <v>20</v>
-      </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>45431</v>
       </c>
       <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16">
         <v>4.5999999999999996</v>
@@ -1161,39 +1162,39 @@
         <v>92</v>
       </c>
       <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" t="s">
         <v>19</v>
       </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16" t="s">
-        <v>20</v>
-      </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1">
         <v>45431</v>
       </c>
       <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17">
         <v>4.0999999999999996</v>
@@ -1205,36 +1206,36 @@
         <v>86</v>
       </c>
       <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17" t="s">
         <v>19</v>
       </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17" t="s">
-        <v>20</v>
-      </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1">
         <v>45431</v>
       </c>
       <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
         <v>16</v>
       </c>
-      <c r="D18" t="s">
-        <v>17</v>
-      </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18">
         <v>3.4</v>
@@ -1246,36 +1247,36 @@
         <v>85</v>
       </c>
       <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="s">
         <v>19</v>
       </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18" t="s">
-        <v>20</v>
-      </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1">
         <v>45431</v>
       </c>
       <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="D19" t="s">
-        <v>17</v>
-      </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19">
         <v>3.7</v>
@@ -1287,36 +1288,36 @@
         <v>86</v>
       </c>
       <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19" t="s">
         <v>19</v>
       </c>
-      <c r="J19">
-        <v>1</v>
-      </c>
-      <c r="K19" t="s">
-        <v>20</v>
-      </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1">
         <v>45431</v>
       </c>
       <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
         <v>16</v>
       </c>
-      <c r="D20" t="s">
-        <v>17</v>
-      </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>4.8</v>
@@ -1328,36 +1329,36 @@
         <v>92</v>
       </c>
       <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" t="s">
         <v>19</v>
       </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20" t="s">
-        <v>20</v>
-      </c>
       <c r="M20">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1">
         <v>45431</v>
       </c>
       <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
         <v>16</v>
       </c>
-      <c r="D21" t="s">
-        <v>17</v>
-      </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21">
         <v>4.9000000000000004</v>
@@ -1369,36 +1370,36 @@
         <v>92</v>
       </c>
       <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
         <v>19</v>
       </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>20</v>
-      </c>
       <c r="M21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1">
         <v>45431</v>
       </c>
       <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
         <v>16</v>
       </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22">
         <v>4.5</v>
@@ -1410,36 +1411,36 @@
         <v>96</v>
       </c>
       <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
         <v>19</v>
       </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22" t="s">
-        <v>20</v>
-      </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1">
         <v>45431</v>
       </c>
       <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
         <v>16</v>
       </c>
-      <c r="D23" t="s">
-        <v>17</v>
-      </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23">
         <v>4.0999999999999996</v>
@@ -1451,36 +1452,36 @@
         <v>90</v>
       </c>
       <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
         <v>19</v>
       </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23" t="s">
-        <v>20</v>
-      </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1">
         <v>45431</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24">
         <v>326</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24">
         <v>4.3</v>
@@ -1492,36 +1493,36 @@
         <v>83</v>
       </c>
       <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
         <v>19</v>
       </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24" t="s">
-        <v>20</v>
-      </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1">
         <v>45431</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25">
         <v>326</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25">
         <v>3.9</v>
@@ -1533,39 +1534,39 @@
         <v>86</v>
       </c>
       <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25" t="s">
         <v>19</v>
       </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25" t="s">
-        <v>20</v>
-      </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="1">
         <v>45431</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26">
         <v>326</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26">
         <v>4.8</v>
@@ -1577,39 +1578,39 @@
         <v>73</v>
       </c>
       <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" t="s">
         <v>19</v>
       </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26" t="s">
-        <v>20</v>
-      </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1">
         <v>45431</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27">
         <v>326</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27">
         <v>3.8</v>
@@ -1621,36 +1622,36 @@
         <v>93</v>
       </c>
       <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27" t="s">
         <v>19</v>
       </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27" t="s">
-        <v>20</v>
-      </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1">
         <v>45440</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28">
         <v>4.5</v>
@@ -1662,13 +1663,13 @@
         <v>97</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J28">
         <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L28">
         <v>22.3</v>
@@ -1677,27 +1678,27 @@
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="1">
         <v>45440</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29">
         <v>4.4000000000000004</v>
@@ -1709,13 +1710,13 @@
         <v>92</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L29">
         <v>22.3</v>
@@ -1724,27 +1725,27 @@
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" s="1">
         <v>45467</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30">
         <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F30">
         <v>6.5</v>
@@ -1756,13 +1757,13 @@
         <v>94</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L30">
         <v>26.4</v>
@@ -1771,27 +1772,27 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B31" s="1">
         <v>45467</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31">
         <v>202</v>
       </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31">
         <v>4.4000000000000004</v>
@@ -1803,13 +1804,13 @@
         <v>90</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L31">
         <v>26.4</v>
@@ -1818,27 +1819,27 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B32" s="1">
         <v>45467</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32">
         <v>202</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32">
         <v>4.9000000000000004</v>
@@ -1850,13 +1851,13 @@
         <v>97</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L32">
         <v>26.4</v>
@@ -1865,27 +1866,27 @@
         <v>1</v>
       </c>
       <c r="N32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" s="1">
         <v>45467</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D33">
         <v>202</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33">
         <v>5.5</v>
@@ -1897,13 +1898,13 @@
         <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L33">
         <v>26.4</v>
@@ -1912,27 +1913,27 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" s="1">
         <v>45478</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F34">
         <v>5.27</v>
@@ -1944,13 +1945,13 @@
         <v>94</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L34">
         <v>27.4</v>
@@ -1959,27 +1960,27 @@
         <v>1</v>
       </c>
       <c r="N34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="1">
         <v>45478</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F35">
         <v>5.18</v>
@@ -1991,13 +1992,13 @@
         <v>94</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L35">
         <v>27.4</v>
@@ -2006,27 +2007,27 @@
         <v>1</v>
       </c>
       <c r="N35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B36" s="1">
         <v>45478</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36">
         <v>5.42</v>
@@ -2038,13 +2039,13 @@
         <v>95</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L36">
         <v>27.4</v>
@@ -2053,27 +2054,27 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37" s="1">
         <v>45478</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F37">
         <v>5.4</v>
@@ -2085,13 +2086,13 @@
         <v>96</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L37">
         <v>27.4</v>
@@ -2100,27 +2101,27 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1">
         <v>45478</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38">
         <v>5.62</v>
@@ -2132,13 +2133,13 @@
         <v>96</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L38">
         <v>27.4</v>
@@ -2147,27 +2148,27 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B39" s="1">
         <v>45478</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F39">
         <v>5.14</v>
@@ -2179,13 +2180,13 @@
         <v>96</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L39">
         <v>27.4</v>
@@ -2194,27 +2195,27 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40" s="1">
         <v>45478</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F40">
         <v>4.78</v>
@@ -2226,13 +2227,13 @@
         <v>95</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J40">
         <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L40">
         <v>27.4</v>
@@ -2241,27 +2242,27 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B41" s="1">
         <v>45478</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41">
         <v>5.37</v>
@@ -2273,13 +2274,13 @@
         <v>93</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L41">
         <v>27.4</v>
@@ -2288,27 +2289,27 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" s="1">
         <v>45478</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F42">
         <v>5.91</v>
@@ -2320,13 +2321,13 @@
         <v>101</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L42">
         <v>27.4</v>
@@ -2335,27 +2336,27 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B43" s="1">
         <v>45478</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F43">
         <v>4.75</v>
@@ -2367,13 +2368,13 @@
         <v>91</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L43">
         <v>27.4</v>
@@ -2382,27 +2383,27 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="1">
         <v>45478</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F44">
         <v>4.8</v>
@@ -2414,13 +2415,13 @@
         <v>99</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L44">
         <v>27.4</v>
@@ -2429,27 +2430,27 @@
         <v>1</v>
       </c>
       <c r="N44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45" s="1">
         <v>45478</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45">
         <v>5.31</v>
@@ -2461,13 +2462,13 @@
         <v>98</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L45">
         <v>27.4</v>
@@ -2476,27 +2477,27 @@
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" s="1">
         <v>45478</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F46">
         <v>5.64</v>
@@ -2508,13 +2509,13 @@
         <v>93</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L46">
         <v>27.4</v>
@@ -2523,27 +2524,27 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B47" s="1">
         <v>45478</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D47">
         <v>293</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F47">
         <v>4.83</v>
@@ -2555,13 +2556,13 @@
         <v>94</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L47">
         <v>27.4</v>
@@ -2570,27 +2571,27 @@
         <v>1</v>
       </c>
       <c r="N47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" s="1">
         <v>45492</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F48">
         <v>4.58</v>
@@ -2602,13 +2603,13 @@
         <v>97</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J48">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L48">
         <v>25.1</v>
@@ -2617,27 +2618,27 @@
         <v>1</v>
       </c>
       <c r="N48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49" s="1">
         <v>45492</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F49">
         <v>5.22</v>
@@ -2649,13 +2650,13 @@
         <v>95</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J49">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L49">
         <v>25.1</v>
@@ -2664,27 +2665,27 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" s="1">
         <v>45492</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F50">
         <v>4.92</v>
@@ -2696,13 +2697,13 @@
         <v>96</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L50">
         <v>25.1</v>
@@ -2711,27 +2712,27 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51" s="1">
         <v>45492</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F51">
         <v>4.99</v>
@@ -2743,13 +2744,13 @@
         <v>97</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J51">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L51">
         <v>25.1</v>
@@ -2758,27 +2759,27 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B52" s="1">
         <v>45492</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F52">
         <v>4.01</v>
@@ -2790,13 +2791,13 @@
         <v>69</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L52">
         <v>25.1</v>
@@ -2805,27 +2806,27 @@
         <v>1</v>
       </c>
       <c r="N52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53" s="1">
         <v>45492</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F53">
         <v>4.18</v>
@@ -2837,13 +2838,13 @@
         <v>89</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J53">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L53">
         <v>25.1</v>
@@ -2852,27 +2853,27 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" s="1">
         <v>45492</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54">
         <v>196</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F54">
         <v>5.35</v>
@@ -2884,13 +2885,13 @@
         <v>100</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J54">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L54">
         <v>25.1</v>
@@ -2899,27 +2900,27 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B55" s="1">
         <v>45517</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55">
         <v>3.99</v>
@@ -2931,13 +2932,13 @@
         <v>86</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J55">
         <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L55">
         <v>25</v>
@@ -2946,27 +2947,27 @@
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B56" s="1">
         <v>45517</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F56">
         <v>3.58</v>
@@ -2978,13 +2979,13 @@
         <v>94</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56">
         <v>3</v>
       </c>
       <c r="K56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L56">
         <v>25</v>
@@ -2993,27 +2994,27 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" s="1">
         <v>45517</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F57">
         <v>4.53</v>
@@ -3025,13 +3026,13 @@
         <v>94</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J57">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L57">
         <v>25</v>
@@ -3040,27 +3041,27 @@
         <v>1</v>
       </c>
       <c r="N57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B58" s="1">
         <v>45517</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F58">
         <v>4.84</v>
@@ -3072,13 +3073,13 @@
         <v>102</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J58">
         <v>4</v>
       </c>
       <c r="K58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L58">
         <v>25</v>
@@ -3087,27 +3088,27 @@
         <v>1</v>
       </c>
       <c r="N58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B59" s="1">
         <v>45517</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F59">
         <v>4.59</v>
@@ -3119,13 +3120,13 @@
         <v>97</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J59">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L59">
         <v>25</v>
@@ -3134,27 +3135,27 @@
         <v>1</v>
       </c>
       <c r="N59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B60" s="1">
         <v>45517</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F60">
         <v>3.8</v>
@@ -3166,13 +3167,13 @@
         <v>85</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J60">
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L60">
         <v>25</v>
@@ -3181,27 +3182,27 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B61" s="1">
         <v>45517</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F61">
         <v>4.08</v>
@@ -3213,13 +3214,13 @@
         <v>91</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61">
         <v>2</v>
       </c>
       <c r="K61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L61">
         <v>25</v>
@@ -3228,27 +3229,27 @@
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62" s="1">
         <v>45517</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F62">
         <v>3.99</v>
@@ -3260,13 +3261,13 @@
         <v>94</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J62">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L62">
         <v>25</v>
@@ -3275,27 +3276,27 @@
         <v>1</v>
       </c>
       <c r="N62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B63" s="1">
         <v>45517</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F63">
         <v>4.29</v>
@@ -3307,13 +3308,13 @@
         <v>97</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J63">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L63">
         <v>25</v>
@@ -3322,27 +3323,27 @@
         <v>0</v>
       </c>
       <c r="N63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B64" s="1">
         <v>45517</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F64">
         <v>4.75</v>
@@ -3354,13 +3355,13 @@
         <v>103</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J64">
         <v>3</v>
       </c>
       <c r="K64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L64">
         <v>25</v>
@@ -3369,27 +3370,27 @@
         <v>0</v>
       </c>
       <c r="N64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65" s="1">
         <v>45517</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F65">
         <v>4.46</v>
@@ -3401,13 +3402,13 @@
         <v>96</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J65">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L65">
         <v>25</v>
@@ -3416,27 +3417,27 @@
         <v>1</v>
       </c>
       <c r="N65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B66" s="1">
         <v>45517</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F66">
         <v>4.24</v>
@@ -3448,13 +3449,13 @@
         <v>96</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J66">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L66">
         <v>25</v>
@@ -3463,27 +3464,27 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B67" s="1">
         <v>45517</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F67">
         <v>4.1399999999999997</v>
@@ -3495,13 +3496,13 @@
         <v>92</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J67">
         <v>3</v>
       </c>
       <c r="K67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L67">
         <v>25</v>
@@ -3510,15 +3511,10 @@
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O67" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K69">
-        <v>0.25757575760000001</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
